--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527D21ED-C019-43A8-927F-14B93C3796A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EFE94D-EFC6-4910-AA6A-34D39376B0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8060" yWindow="3000" windowWidth="23040" windowHeight="12070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,18 +55,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>a1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>b1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>b2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>a2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -88,6 +80,28 @@
   </si>
   <si>
     <t>program_next</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zsasda11111111111111</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qqqqqqqqqqqqqqqqqqq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>&amp;</t>
+  </si>
+  <si>
+    <t>@</t>
+  </si>
+  <si>
+    <t>sound=bgm1, ani=ani1,background=bg1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sound=bgm2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -416,23 +430,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.4140625" customWidth="1"/>
-    <col min="3" max="3" width="24.75" customWidth="1"/>
-    <col min="4" max="5" width="23.9140625" customWidth="1"/>
-    <col min="6" max="6" width="27.08203125" customWidth="1"/>
-    <col min="7" max="8" width="11.5" customWidth="1"/>
+    <col min="1" max="1" width="15.21875" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" customWidth="1"/>
+    <col min="4" max="5" width="23.88671875" customWidth="1"/>
+    <col min="6" max="6" width="27.109375" customWidth="1"/>
+    <col min="7" max="7" width="43.5546875" customWidth="1"/>
+    <col min="8" max="8" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -441,19 +456,19 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -479,30 +494,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+      <c r="E3" s="1"/>
+      <c r="G3" t="s">
+        <v>18</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -510,62 +517,73 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
       <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EFE94D-EFC6-4910-AA6A-34D39376B0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919F818F-096F-4139-9D43-F8FF6800159F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="4272" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,22 +67,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>program_ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>program_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>image_size</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>program_next</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>zsasda11111111111111</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -102,6 +90,18 @@
   </si>
   <si>
     <t>sound=bgm2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>process_next</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>process_ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>process_type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -444,10 +444,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -456,7 +456,7 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -465,7 +465,7 @@
         <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -501,9 +501,14 @@
       <c r="B3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -517,7 +522,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -529,7 +534,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -540,10 +545,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -563,7 +568,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -583,6 +588,15 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="H7">
         <v>4</v>
       </c>
     </row>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919F818F-096F-4139-9D43-F8FF6800159F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C58165A-1BA8-41A3-B371-BF871CA72D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="4272" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4872" yWindow="4272" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,10 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>image_name</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -51,18 +47,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>&amp;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>b1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>command</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -71,28 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>zsasda11111111111111</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qqqqqqqqqqqqqqqqqqq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>&amp;</t>
-  </si>
-  <si>
-    <t>@</t>
-  </si>
-  <si>
-    <t>sound=bgm1, ani=ani1,background=bg1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sound=bgm2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>process_next</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -102,6 +64,82 @@
   </si>
   <si>
     <t>process_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>father</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>好的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qaq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mother</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classmates</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classmate1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>唉唉唉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈哈哈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clearimage=1,clearimage=0,continue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clearimage=2,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio=bgm1, background=dormitory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio=click1,background=desk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio=bgm1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -430,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -444,28 +482,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
       <c r="H1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -482,10 +520,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
         <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
@@ -499,7 +537,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -508,7 +546,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -519,22 +557,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -545,19 +583,19 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>3</v>
@@ -568,19 +606,22 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>28</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -590,6 +631,15 @@
       <c r="A7">
         <v>4</v>
       </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
@@ -597,6 +647,58 @@
         <v>1</v>
       </c>
       <c r="H7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9">
         <v>4</v>
       </c>
     </row>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C58165A-1BA8-41A3-B371-BF871CA72D76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0157F2D5-7372-460D-83A6-05925CD89F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4872" yWindow="4272" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="444" yWindow="3396" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -127,19 +128,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>clearimage=2,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>audio=bgm1, background=dormitory</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>audio=click1,background=desk</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>audio=bgm1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clearimage=2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>background=desk,interaction=Interaction_test</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -476,7 +477,7 @@
     <col min="3" max="3" width="24.77734375" customWidth="1"/>
     <col min="4" max="5" width="23.88671875" customWidth="1"/>
     <col min="6" max="6" width="27.109375" customWidth="1"/>
-    <col min="7" max="7" width="43.5546875" customWidth="1"/>
+    <col min="7" max="7" width="55.44140625" customWidth="1"/>
     <col min="8" max="8" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -546,7 +547,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -572,7 +573,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -621,7 +622,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -696,7 +697,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H9">
         <v>4</v>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0157F2D5-7372-460D-83A6-05925CD89F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16B3A99-6AA2-485B-8E06-C9669BCFED48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="444" yWindow="3396" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -140,7 +140,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>background=desk,interaction=Interaction_test</t>
+    <t>background=desk,interaction=Interaction_LimitedTimeToChoose</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -5,18 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\顾\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16B3A99-6AA2-485B-8E06-C9669BCFED48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D2C913-7724-498A-88BC-9F7DAA6C66BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="444" yWindow="3396" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,22 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>image_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>image_position</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>command</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>image_size</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>process_next</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -64,14 +47,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>process_type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>father</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>啊？</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -80,18 +55,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>b</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>qaq</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -100,22 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>mother</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>classmates</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>classmate1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>唉唉唉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -124,23 +71,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>clearimage=1,clearimage=0,continue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio=bgm1, background=dormitory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>audio=bgm1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>clearimage=2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>background=desk,interaction=Interaction_LimitedTimeToChoose</t>
+    <t>image</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>background</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>audio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>command_after</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>command_before</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>option;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imagefade;audiofade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imageflash;audioflash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classmate1,1,1;classmate2,2,0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classroom</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>father,0,0.7;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clearimage,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -473,38 +452,39 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="24.77734375" customWidth="1"/>
-    <col min="4" max="5" width="23.88671875" customWidth="1"/>
-    <col min="6" max="6" width="27.109375" customWidth="1"/>
-    <col min="7" max="7" width="55.44140625" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="29" customWidth="1"/>
+    <col min="4" max="4" width="30.88671875" customWidth="1"/>
+    <col min="5" max="5" width="23.88671875" customWidth="1"/>
+    <col min="6" max="6" width="18.109375" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
     <col min="8" max="8" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -521,10 +501,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
@@ -538,16 +518,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -558,23 +538,12 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E4" s="1"/>
       <c r="H4">
         <v>3</v>
       </c>
@@ -584,20 +553,12 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="F5">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="E5" s="1"/>
       <c r="H5">
         <v>3</v>
       </c>
@@ -607,22 +568,17 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" t="s">
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -632,21 +588,10 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
       <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="E7" s="1"/>
       <c r="H7">
         <v>5</v>
       </c>
@@ -655,24 +600,13 @@
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
       <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
         <v>22</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>24</v>
-      </c>
+      <c r="E8" s="1"/>
       <c r="H8">
         <v>6</v>
       </c>
@@ -681,23 +615,12 @@
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
       <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="s">
-        <v>27</v>
+      <c r="E9" s="1"/>
+      <c r="F9" t="s">
+        <v>21</v>
       </c>
       <c r="H9">
         <v>4</v>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\顾\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D2C913-7724-498A-88BC-9F7DAA6C66BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FFF1BC-03E2-4C69-BB65-0E1C45C92E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -107,10 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>classroom</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bgm1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -120,6 +116,30 @@
   </si>
   <si>
     <t>clearimage,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classmates,1.3,3.1,0.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LimitTimeToChoose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>option;interaction,LimitedTimeToChoose</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ScreenShake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>classroom,0;dormitory,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clearimage,classmates;ScreenShake</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -458,7 +478,7 @@
     <col min="5" max="5" width="23.88671875" customWidth="1"/>
     <col min="6" max="6" width="18.109375" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="17.77734375" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -524,10 +544,10 @@
         <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
         <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -538,12 +558,18 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
       <c r="E4" s="1"/>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
       <c r="H4">
         <v>3</v>
       </c>
@@ -575,10 +601,10 @@
       </c>
       <c r="E6" s="1"/>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -588,10 +614,16 @@
       <c r="A7">
         <v>4</v>
       </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="1"/>
+      <c r="G7" t="s">
+        <v>26</v>
+      </c>
       <c r="H7">
         <v>5</v>
       </c>
@@ -600,13 +632,19 @@
       <c r="A8">
         <v>5</v>
       </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1"/>
+      <c r="G8" t="s">
+        <v>28</v>
+      </c>
       <c r="H8">
         <v>6</v>
       </c>
@@ -620,7 +658,7 @@
       </c>
       <c r="E9" s="1"/>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9">
         <v>4</v>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FFF1BC-03E2-4C69-BB65-0E1C45C92E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503C2EE1-6617-418C-91CB-33F172111EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6768" yWindow="2232" windowWidth="20016" windowHeight="12036" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -131,15 +131,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ScreenShake</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>classroom,0;dormitory,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>clearimage,classmates;ScreenShake</t>
+    <t>interaction,viewchange;uifade;hideui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clearimage,classmates;effect,ScreenShake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect,ScreenShake;imagefadetime,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -468,11 +472,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
-    <col min="2" max="2" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="38.44140625" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
     <col min="4" max="4" width="30.88671875" customWidth="1"/>
     <col min="5" max="5" width="23.88671875" customWidth="1"/>
@@ -544,7 +548,7 @@
         <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -621,9 +625,6 @@
         <v>8</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
       <c r="H7">
         <v>5</v>
       </c>
@@ -633,7 +634,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -661,7 +662,18 @@
         <v>20</v>
       </c>
       <c r="H9">
-        <v>4</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503C2EE1-6617-418C-91CB-33F172111EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01182BCD-8B44-436F-A476-6A774A7F676E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6768" yWindow="2232" windowWidth="20016" windowHeight="12036" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -135,15 +135,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>interaction,viewchange;uifade;hideui</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>clearimage,classmates;effect,ScreenShake</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>effect,ScreenShake;imagefadetime,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dormitory,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imagefade;audiofade,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interaction,DrawBook</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effect,Blink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>showui</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>interaction,viewchange</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -472,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.21875" customWidth="1"/>
@@ -542,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
@@ -570,7 +590,9 @@
       <c r="D4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="G4" t="s">
         <v>24</v>
       </c>
@@ -634,7 +656,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -644,7 +666,7 @@
       </c>
       <c r="E8" s="1"/>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -654,6 +676,9 @@
       <c r="A9">
         <v>6</v>
       </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
@@ -670,10 +695,43 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H10">
         <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="H13">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01182BCD-8B44-436F-A476-6A774A7F676E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9574996-5FE6-4ACA-A8A3-F250E1176D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2556" windowWidth="27648" windowHeight="14004" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -155,15 +155,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Effect,Blink</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>showui</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>interaction,viewchange</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -682,7 +682,9 @@
       <c r="C9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="F9" t="s">
         <v>20</v>
       </c>
@@ -695,7 +697,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10">
         <v>8</v>
@@ -717,10 +719,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
         <v>32</v>
-      </c>
-      <c r="G12" t="s">
-        <v>33</v>
       </c>
       <c r="H12">
         <v>10</v>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9574996-5FE6-4ACA-A8A3-F250E1176D19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64899EDC-E28C-46EB-9059-E08AD0DCE1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2556" windowWidth="27648" windowHeight="14004" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -95,10 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>imagefade;audiofade</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>imageflash;audioflash</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,10 +107,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>father,0,0.7;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>clearimage,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,7 +155,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>w</t>
+    <t>father_sad,0,0.7;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imagefade;audiofade;hideui;effect,Blink</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -562,16 +558,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -582,19 +578,19 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -620,17 +616,17 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
         <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -641,7 +637,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -656,17 +652,17 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E8" s="1"/>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -677,16 +673,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -697,7 +693,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H10">
         <v>8</v>
@@ -708,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H11">
         <v>9</v>
@@ -718,11 +714,8 @@
       <c r="A12">
         <v>9</v>
       </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
       <c r="G12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H12">
         <v>10</v>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64899EDC-E28C-46EB-9059-E08AD0DCE1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C51F79A-0FBA-4F06-B44E-E115616E447E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2556" windowWidth="27648" windowHeight="14004" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -95,18 +95,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>imagefade;audiofade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>imageflash;audioflash</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>classmate1,1,1;classmate2,2,0.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>clearimage,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -115,10 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LimitTimeToChoose</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>option;interaction,LimitedTimeToChoose</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -139,14 +131,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>imagefade;audiofade,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>interaction,DrawBook</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>showui</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -160,6 +144,26 @@
   </si>
   <si>
     <t>imagefade;audiofade;hideui;effect,Blink</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect,ScreenShake;imagefadetime,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aaa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>d</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ddfasfa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>clearimage,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -558,17 +562,9 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="E3" s="1"/>
       <c r="H3">
         <v>1</v>
       </c>
@@ -578,19 +574,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -616,17 +609,14 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>19</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -637,7 +627,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -652,17 +642,17 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1"/>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -673,16 +663,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="G9" t="s">
+        <v>34</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -693,7 +683,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H10">
         <v>8</v>
@@ -703,8 +693,8 @@
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>29</v>
+      <c r="C11" t="s">
+        <v>31</v>
       </c>
       <c r="H11">
         <v>9</v>
@@ -714,8 +704,11 @@
       <c r="A12">
         <v>9</v>
       </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -724,6 +717,9 @@
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>33</v>
       </c>
       <c r="H13">
         <v>11</v>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C51F79A-0FBA-4F06-B44E-E115616E447E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC4898F-4CA6-4D73-9715-D6490F020278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2556" windowWidth="27648" windowHeight="14004" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -95,10 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>imagefade;audiofade</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>imageflash;audioflash</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -164,6 +160,10 @@
   </si>
   <si>
     <t>clearimage,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>imagefade</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1"/>
       <c r="H3">
@@ -574,16 +574,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -609,14 +609,14 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="1"/>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -627,7 +627,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -642,17 +642,17 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1"/>
       <c r="G8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -663,16 +663,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -683,7 +683,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H10">
         <v>8</v>
@@ -694,7 +694,7 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H11">
         <v>9</v>
@@ -705,10 +705,10 @@
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H12">
         <v>10</v>
@@ -719,7 +719,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H13">
         <v>11</v>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC4898F-4CA6-4D73-9715-D6490F020278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB60ACA-0583-4978-9D6E-2EC93FC96042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2556" windowWidth="27648" windowHeight="14004" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB60ACA-0583-4978-9D6E-2EC93FC96042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA586EDC-1F35-4F95-97BC-B4AE551F195C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2556" windowWidth="27648" windowHeight="14004" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -164,6 +164,10 @@
   </si>
   <si>
     <t>imagefade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>changeprocess,4,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -585,6 +589,9 @@
       <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
       <c r="H4">
         <v>3</v>
       </c>

--- a/Assets/Resources/storyline.xlsx
+++ b/Assets/Resources/storyline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Files\Unity\Not have a name yet\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA586EDC-1F35-4F95-97BC-B4AE551F195C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BBFBB8-CC63-4979-B5B1-4148573231D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2556" windowWidth="27648" windowHeight="14004" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -167,7 +167,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>changeprocess,4,3</t>
+    <t>interaction,End</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -589,9 +589,6 @@
       <c r="E4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G4" t="s">
-        <v>35</v>
-      </c>
       <c r="H4">
         <v>3</v>
       </c>
@@ -727,6 +724,9 @@
       </c>
       <c r="C13" t="s">
         <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
       </c>
       <c r="H13">
         <v>11</v>
